--- a/StructureDefinition-VunsPatient.xlsx
+++ b/StructureDefinition-VunsPatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$96</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3158" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3599" uniqueCount="597">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T10:39:09+02:00</t>
+    <t>2025-08-04T16:28:32+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -324,13 +324,230 @@
 </t>
   </si>
   <si>
-    <t>Patient.implicitRules</t>
+    <t>Patient.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Patient.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Patient.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Patient.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Patient.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Patient.meta.profile</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Patient.meta.profile:vunsPatient</t>
+  </si>
+  <si>
+    <t>vunsPatient</t>
+  </si>
+  <si>
+    <t>Patient.meta.profile:bePatient</t>
+  </si>
+  <si>
+    <t>bePatient</t>
+  </si>
+  <si>
+    <t>https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-patient</t>
+  </si>
+  <si>
+    <t>Patient.meta.profile:euIpsPatient</t>
+  </si>
+  <si>
+    <t>euIpsPatient</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/ips/StructureDefinition/Patient-uv-ips</t>
+  </si>
+  <si>
+    <t>Patient.meta.profile:chulPatient</t>
+  </si>
+  <si>
+    <t>chulPatient</t>
+  </si>
+  <si>
+    <t>https://terminology.chuliege.be/fhir/StructureDefinition/chul-patient</t>
+  </si>
+  <si>
+    <t>Patient.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Patient.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Patient.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -426,28 +643,13 @@
     <t>Patient.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
     <t>Extension</t>
   </si>
   <si>
     <t>An Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace</t>
@@ -472,32 +674,14 @@
     <t>Patient.extension.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Patient.extension:birthPlace.extension</t>
   </si>
   <si>
     <t>Patient.extension.extension</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace.url</t>
@@ -595,18 +779,11 @@
     <t>Patient.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -710,17 +887,7 @@
     <t>Patient.name.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Patient.name.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Patient.name.extension:name-absent-reason</t>
@@ -1089,15 +1256,7 @@
     <t>Time period when the contact point was/is in use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>ContactPoint.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Patient.telecom:email</t>
@@ -1195,6 +1354,12 @@
     <t>Patient.birthDate.id</t>
   </si>
   <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
     <t>Patient.birthDate.extension</t>
   </si>
   <si>
@@ -1211,6 +1376,9 @@
   </si>
   <si>
     <t>Primitive value for date</t>
+  </si>
+  <si>
+    <t>The actual value</t>
   </si>
   <si>
     <t>date.value</t>
@@ -1279,9 +1447,6 @@
   </si>
   <si>
     <t>Most, if not all systems capture it.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>The domestic partnership status of a person.</t>
@@ -2026,7 +2191,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO84"/>
+  <dimension ref="A1:AO96"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.40234375" customWidth="true" bestFit="true"/>
@@ -2053,7 +2218,7 @@
     <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="78.75390625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.77734375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.28125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
@@ -2565,10 +2730,10 @@
         <v>19</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>101</v>
@@ -2579,9 +2744,7 @@
       <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>19</v>
@@ -2630,7 +2793,7 @@
         <v>19</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2642,10 +2805,10 @@
         <v>19</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>19</v>
@@ -2669,14 +2832,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>19</v>
@@ -2688,16 +2851,16 @@
         <v>19</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2723,46 +2886,46 @@
         <v>19</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>19</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>19</v>
@@ -2779,14 +2942,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2802,10 +2965,10 @@
         <v>19</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>118</v>
@@ -2879,7 +3042,7 @@
         <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>19</v>
@@ -2896,21 +3059,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>19</v>
@@ -2919,19 +3082,19 @@
         <v>19</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2981,22 +3144,22 @@
         <v>19</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>19</v>
@@ -3013,10 +3176,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3027,7 +3190,7 @@
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>19</v>
@@ -3036,18 +3199,20 @@
         <v>19</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>19</v>
@@ -3084,29 +3249,31 @@
         <v>19</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>19</v>
@@ -3126,23 +3293,21 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>19</v>
@@ -3151,18 +3316,20 @@
         <v>19</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>19</v>
@@ -3199,19 +3366,17 @@
         <v>19</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AC10" s="2"/>
       <c r="AD10" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3223,7 +3388,7 @@
         <v>19</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>19</v>
@@ -3243,18 +3408,20 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>87</v>
@@ -3266,18 +3433,20 @@
         <v>19</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>19</v>
@@ -3287,7 +3456,7 @@
         <v>19</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>19</v>
@@ -3326,22 +3495,22 @@
         <v>19</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>19</v>
@@ -3358,21 +3527,23 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>19</v>
@@ -3381,18 +3552,20 @@
         <v>19</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>19</v>
@@ -3402,7 +3575,7 @@
         <v>19</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>19</v>
@@ -3429,19 +3602,19 @@
         <v>19</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3453,7 +3626,7 @@
         <v>19</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>19</v>
@@ -3473,12 +3646,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>19</v>
       </c>
@@ -3496,19 +3671,19 @@
         <v>19</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3516,10 +3691,10 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>19</v>
@@ -3558,22 +3733,22 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>19</v>
@@ -3590,12 +3765,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>19</v>
       </c>
@@ -3613,18 +3790,20 @@
         <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>19</v>
@@ -3634,7 +3813,7 @@
         <v>19</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>19</v>
@@ -3673,22 +3852,22 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>19</v>
@@ -3705,14 +3884,12 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>19</v>
       </c>
@@ -3730,18 +3907,20 @@
         <v>19</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>19</v>
@@ -3766,13 +3945,13 @@
         <v>19</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>19</v>
+        <v>159</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>19</v>
@@ -3790,7 +3969,7 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3802,7 +3981,7 @@
         <v>19</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>19</v>
@@ -3822,14 +4001,12 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>19</v>
       </c>
@@ -3847,18 +4024,20 @@
         <v>19</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>19</v>
@@ -3883,13 +4062,13 @@
         <v>19</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>19</v>
+        <v>166</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
@@ -3907,7 +4086,7 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3919,7 +4098,7 @@
         <v>19</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>19</v>
@@ -3939,14 +4118,12 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>19</v>
       </c>
@@ -3955,27 +4132,29 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>19</v>
@@ -4024,19 +4203,19 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>19</v>
@@ -4056,46 +4235,44 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>19</v>
       </c>
@@ -4119,13 +4296,13 @@
         <v>19</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>19</v>
+        <v>182</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>19</v>
@@ -4143,22 +4320,22 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>19</v>
@@ -4175,21 +4352,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>19</v>
@@ -4198,21 +4375,21 @@
         <v>19</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>19</v>
       </c>
@@ -4260,13 +4437,13 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>19</v>
@@ -4275,16 +4452,16 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>197</v>
+        <v>19</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>19</v>
@@ -4292,52 +4469,48 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="Q20" t="s" s="2">
-        <v>206</v>
-      </c>
+      <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
         <v>19</v>
       </c>
@@ -4381,28 +4554,28 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>19</v>
@@ -4413,10 +4586,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4424,35 +4597,31 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>19</v>
       </c>
@@ -4488,19 +4657,17 @@
         <v>19</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4512,19 +4679,19 @@
         <v>19</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>215</v>
+        <v>116</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>218</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>19</v>
@@ -4532,12 +4699,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>19</v>
       </c>
@@ -4558,13 +4727,13 @@
         <v>19</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>147</v>
+        <v>208</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4615,22 +4784,22 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>19</v>
@@ -4647,21 +4816,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>19</v>
@@ -4673,17 +4842,15 @@
         <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>102</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>19</v>
@@ -4720,34 +4887,34 @@
         <v>19</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>19</v>
@@ -4764,14 +4931,12 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>19</v>
       </c>
@@ -4780,7 +4945,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>19</v>
@@ -4792,13 +4957,13 @@
         <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>226</v>
+        <v>108</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4837,19 +5002,19 @@
         <v>19</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4861,10 +5026,10 @@
         <v>19</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>19</v>
@@ -4881,10 +5046,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4892,7 +5057,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>87</v>
@@ -4901,32 +5066,30 @@
         <v>19</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>19</v>
@@ -4944,13 +5107,13 @@
         <v>19</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>236</v>
+        <v>19</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>19</v>
@@ -4968,10 +5131,10 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>87</v>
@@ -4980,10 +5143,10 @@
         <v>19</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>19</v>
@@ -4992,7 +5155,7 @@
         <v>19</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>239</v>
+        <v>19</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>19</v>
@@ -5000,10 +5163,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5011,7 +5174,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>87</v>
@@ -5023,23 +5186,19 @@
         <v>19</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>19</v>
       </c>
@@ -5087,7 +5246,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5096,13 +5255,13 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>19</v>
+        <v>227</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>19</v>
@@ -5111,7 +5270,7 @@
         <v>19</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>19</v>
@@ -5119,21 +5278,23 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="D27" t="s" s="2">
-        <v>249</v>
+        <v>19</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>19</v>
@@ -5142,20 +5303,18 @@
         <v>19</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -5168,7 +5327,7 @@
         <v>19</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>253</v>
+        <v>19</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>19</v>
@@ -5204,22 +5363,22 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>203</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>255</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>19</v>
@@ -5228,7 +5387,7 @@
         <v>19</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>256</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>19</v>
@@ -5236,14 +5395,16 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>258</v>
+        <v>19</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5259,20 +5420,18 @@
         <v>19</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -5321,7 +5480,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5333,10 +5492,10 @@
         <v>19</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>263</v>
+        <v>19</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>19</v>
@@ -5345,7 +5504,7 @@
         <v>19</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>19</v>
@@ -5353,12 +5512,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>19</v>
       </c>
@@ -5376,16 +5537,16 @@
         <v>19</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5436,7 +5597,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5448,10 +5609,10 @@
         <v>19</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>269</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>19</v>
@@ -5460,7 +5621,7 @@
         <v>19</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>270</v>
+        <v>19</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>19</v>
@@ -5468,14 +5629,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5488,22 +5649,26 @@
         <v>19</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
       </c>
@@ -5551,7 +5716,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5563,10 +5728,10 @@
         <v>19</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>19</v>
@@ -5575,7 +5740,7 @@
         <v>19</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>19</v>
@@ -5583,10 +5748,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5597,7 +5762,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>19</v>
@@ -5609,17 +5774,17 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -5668,13 +5833,13 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>19</v>
@@ -5683,16 +5848,16 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>19</v>
+        <v>255</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>19</v>
@@ -5700,10 +5865,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5711,39 +5876,41 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>259</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="Q32" s="2"/>
+      <c r="Q32" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="R32" t="s" s="2">
         <v>19</v>
       </c>
@@ -5775,23 +5942,25 @@
         <v>19</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>19</v>
@@ -5800,16 +5969,16 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>294</v>
+        <v>105</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>295</v>
+        <v>19</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>19</v>
@@ -5817,14 +5986,12 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>19</v>
       </c>
@@ -5845,19 +6012,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -5906,7 +6073,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5918,19 +6085,19 @@
         <v>19</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>272</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>19</v>
@@ -5938,10 +6105,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5964,13 +6131,13 @@
         <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>220</v>
+        <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6021,7 +6188,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6036,7 +6203,7 @@
         <v>19</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>19</v>
@@ -6053,14 +6220,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6079,16 +6246,16 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>222</v>
+        <v>109</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>223</v>
+        <v>110</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6126,19 +6293,19 @@
         <v>19</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6150,10 +6317,10 @@
         <v>19</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>19</v>
@@ -6170,21 +6337,23 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>19</v>
@@ -6193,16 +6362,16 @@
         <v>19</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>280</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6214,7 +6383,7 @@
         <v>19</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>19</v>
@@ -6229,13 +6398,13 @@
         <v>19</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>306</v>
+        <v>19</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>19</v>
@@ -6253,22 +6422,22 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>308</v>
+        <v>115</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>309</v>
+        <v>19</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>19</v>
@@ -6277,7 +6446,7 @@
         <v>19</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>311</v>
+        <v>19</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>19</v>
@@ -6285,10 +6454,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6305,25 +6474,25 @@
         <v>19</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>316</v>
+        <v>286</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6348,13 +6517,13 @@
         <v>19</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>19</v>
+        <v>289</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>19</v>
+        <v>290</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>19</v>
@@ -6372,7 +6541,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6384,10 +6553,10 @@
         <v>19</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>319</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>19</v>
@@ -6396,7 +6565,7 @@
         <v>19</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>19</v>
@@ -6404,10 +6573,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>294</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6424,25 +6593,25 @@
         <v>19</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>19</v>
@@ -6467,13 +6636,13 @@
         <v>19</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>328</v>
+        <v>19</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>329</v>
+        <v>19</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>19</v>
@@ -6491,7 +6660,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6506,7 +6675,7 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>238</v>
+        <v>300</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>19</v>
@@ -6515,7 +6684,7 @@
         <v>19</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>19</v>
@@ -6523,14 +6692,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>332</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>333</v>
+        <v>302</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>19</v>
+        <v>303</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6549,16 +6718,16 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>334</v>
+        <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6572,7 +6741,7 @@
         <v>19</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>19</v>
+        <v>307</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>19</v>
@@ -6608,7 +6777,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6623,7 +6792,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>150</v>
+        <v>309</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>19</v>
@@ -6632,7 +6801,7 @@
         <v>19</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>19</v>
@@ -6640,21 +6809,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>19</v>
+        <v>312</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>19</v>
@@ -6666,16 +6835,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>278</v>
+        <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>342</v>
+        <v>314</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6725,22 +6894,22 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>345</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>19</v>
@@ -6749,7 +6918,7 @@
         <v>19</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>130</v>
+        <v>318</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>19</v>
@@ -6757,26 +6926,24 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>346</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>19</v>
@@ -6785,20 +6952,16 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>287</v>
+        <v>101</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>19</v>
       </c>
@@ -6846,7 +7009,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>285</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6861,16 +7024,16 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>294</v>
+        <v>19</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>19</v>
@@ -6878,10 +7041,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6892,7 +7055,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>19</v>
@@ -6901,16 +7064,16 @@
         <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>220</v>
+        <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>146</v>
+        <v>326</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>147</v>
+        <v>327</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6961,22 +7124,22 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>148</v>
+        <v>328</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>150</v>
+        <v>329</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>19</v>
@@ -6985,7 +7148,7 @@
         <v>19</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>19</v>
@@ -6993,21 +7156,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>19</v>
@@ -7016,21 +7179,21 @@
         <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>132</v>
+        <v>332</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>222</v>
+        <v>333</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
       </c>
@@ -7066,34 +7229,34 @@
         <v>19</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>154</v>
+        <v>336</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>150</v>
+        <v>337</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>19</v>
@@ -7102,7 +7265,7 @@
         <v>19</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>19</v>
+        <v>338</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>19</v>
@@ -7110,10 +7273,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7121,10 +7284,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>87</v>
+        <v>340</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>19</v>
@@ -7136,16 +7299,20 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>341</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
       </c>
@@ -7154,7 +7321,7 @@
         <v>19</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>347</v>
+        <v>19</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>19</v>
@@ -7169,55 +7336,53 @@
         <v>19</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>306</v>
+        <v>19</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>309</v>
+        <v>19</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>19</v>
+        <v>348</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>19</v>
@@ -7225,24 +7390,26 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C45" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="B45" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>19</v>
@@ -7251,19 +7418,19 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>220</v>
+        <v>341</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7312,31 +7479,31 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>352</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>19</v>
+        <v>348</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>19</v>
@@ -7344,10 +7511,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7364,26 +7531,22 @@
         <v>19</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>324</v>
+        <v>102</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>19</v>
       </c>
@@ -7407,13 +7570,13 @@
         <v>19</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>328</v>
+        <v>19</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>329</v>
+        <v>19</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>19</v>
@@ -7431,7 +7594,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>330</v>
+        <v>104</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7443,10 +7606,10 @@
         <v>19</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>238</v>
+        <v>105</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>19</v>
@@ -7455,7 +7618,7 @@
         <v>19</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>331</v>
+        <v>19</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>19</v>
@@ -7466,18 +7629,18 @@
         <v>354</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>19</v>
@@ -7486,19 +7649,19 @@
         <v>19</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>334</v>
+        <v>108</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>335</v>
+        <v>109</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>336</v>
+        <v>110</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>337</v>
+        <v>111</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7536,34 +7699,34 @@
         <v>19</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>338</v>
+        <v>115</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>19</v>
@@ -7572,7 +7735,7 @@
         <v>19</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>19</v>
@@ -7580,10 +7743,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7591,7 +7754,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>87</v>
@@ -7606,17 +7769,15 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>278</v>
+        <v>176</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7626,7 +7787,7 @@
         <v>19</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>19</v>
+        <v>351</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>19</v>
@@ -7641,13 +7802,13 @@
         <v>19</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>19</v>
@@ -7665,7 +7826,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7674,13 +7835,13 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>149</v>
+        <v>363</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>345</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>283</v>
+        <v>364</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>19</v>
@@ -7689,7 +7850,7 @@
         <v>19</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>130</v>
+        <v>365</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>19</v>
@@ -7697,10 +7858,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7723,19 +7884,19 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7760,13 +7921,13 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
@@ -7784,7 +7945,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7796,19 +7957,19 @@
         <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>373</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>19</v>
@@ -7816,10 +7977,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7827,7 +7988,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>87</v>
@@ -7836,25 +7997,25 @@
         <v>19</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>367</v>
+        <v>176</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -7879,13 +8040,13 @@
         <v>19</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>19</v>
+        <v>382</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>19</v>
+        <v>383</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>19</v>
@@ -7903,7 +8064,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7918,27 +8079,27 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>372</v>
+        <v>292</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>373</v>
+        <v>19</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>375</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7958,18 +8119,20 @@
         <v>19</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>220</v>
+        <v>388</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>146</v>
+        <v>389</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -8018,7 +8181,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>148</v>
+        <v>392</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8030,10 +8193,10 @@
         <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>19</v>
@@ -8042,7 +8205,7 @@
         <v>19</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>19</v>
@@ -8050,21 +8213,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>19</v>
@@ -8073,20 +8236,18 @@
         <v>19</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>132</v>
+        <v>332</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>222</v>
+        <v>395</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -8123,34 +8284,34 @@
         <v>19</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>154</v>
+        <v>397</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>150</v>
+        <v>337</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>19</v>
@@ -8159,7 +8320,7 @@
         <v>19</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>19</v>
+        <v>199</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>19</v>
@@ -8167,46 +8328,48 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>339</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>226</v>
+        <v>341</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>380</v>
+        <v>342</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>380</v>
+        <v>343</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>19</v>
       </c>
@@ -8254,7 +8417,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>154</v>
+        <v>339</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8263,22 +8426,22 @@
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>228</v>
+        <v>347</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>19</v>
+        <v>348</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>19</v>
+        <v>349</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>19</v>
@@ -8286,10 +8449,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8312,13 +8475,13 @@
         <v>19</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>367</v>
+        <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>382</v>
+        <v>102</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
+        <v>103</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8369,7 +8532,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>383</v>
+        <v>104</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8384,7 +8547,7 @@
         <v>19</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>19</v>
@@ -8401,46 +8564,44 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>385</v>
+        <v>108</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>386</v>
+        <v>109</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>387</v>
+        <v>110</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>19</v>
       </c>
@@ -8476,43 +8637,43 @@
         <v>19</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>384</v>
+        <v>115</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>390</v>
+        <v>105</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>391</v>
+        <v>19</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>19</v>
@@ -8520,10 +8681,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>392</v>
+        <v>357</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8531,10 +8692,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>19</v>
@@ -8546,20 +8707,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>393</v>
+        <v>358</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>19</v>
       </c>
@@ -8568,7 +8725,7 @@
         <v>19</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>19</v>
+        <v>399</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>19</v>
@@ -8583,13 +8740,13 @@
         <v>19</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>19</v>
@@ -8607,31 +8764,31 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>398</v>
+        <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>19</v>
@@ -8639,10 +8796,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8662,20 +8819,22 @@
         <v>19</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>401</v>
+        <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>404</v>
+        <v>371</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>19</v>
@@ -8700,13 +8859,13 @@
         <v>19</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>405</v>
+        <v>19</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>406</v>
+        <v>19</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>407</v>
+        <v>19</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
@@ -8724,7 +8883,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8736,19 +8895,19 @@
         <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>404</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>409</v>
+        <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>410</v>
+        <v>375</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>19</v>
@@ -8756,10 +8915,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>377</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8776,25 +8935,25 @@
         <v>19</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>412</v>
+        <v>176</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>413</v>
+        <v>378</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>414</v>
+        <v>379</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>415</v>
+        <v>380</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>416</v>
+        <v>381</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>19</v>
@@ -8819,13 +8978,13 @@
         <v>19</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>19</v>
+        <v>382</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>19</v>
+        <v>383</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>19</v>
@@ -8843,7 +9002,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>411</v>
+        <v>384</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8858,16 +9017,16 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>417</v>
+        <v>292</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>19</v>
@@ -8875,10 +9034,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>419</v>
+        <v>387</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8889,7 +9048,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>19</v>
@@ -8898,23 +9057,21 @@
         <v>19</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>420</v>
+        <v>388</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>422</v>
+        <v>390</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>19</v>
       </c>
@@ -8962,13 +9119,13 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>19</v>
@@ -8977,16 +9134,16 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>425</v>
+        <v>105</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>426</v>
+        <v>105</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>19</v>
@@ -8994,10 +9151,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>394</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9008,7 +9165,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>19</v>
@@ -9017,23 +9174,19 @@
         <v>19</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>428</v>
+        <v>332</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>429</v>
+        <v>395</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>19</v>
       </c>
@@ -9081,31 +9234,31 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>433</v>
+        <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>434</v>
+        <v>337</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>19</v>
+        <v>199</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>19</v>
@@ -9113,10 +9266,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9124,31 +9277,35 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>146</v>
+        <v>409</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>19</v>
       </c>
@@ -9172,13 +9329,13 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>19</v>
+        <v>413</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>19</v>
+        <v>414</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>19</v>
@@ -9196,7 +9353,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>148</v>
+        <v>408</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9208,19 +9365,19 @@
         <v>19</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>150</v>
+        <v>415</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>19</v>
+        <v>416</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>19</v>
+        <v>417</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>19</v>
@@ -9228,21 +9385,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>19</v>
@@ -9251,21 +9408,23 @@
         <v>19</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>132</v>
+        <v>419</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>222</v>
+        <v>420</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>223</v>
+        <v>421</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>19</v>
       </c>
@@ -9313,78 +9472,74 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>154</v>
+        <v>418</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>150</v>
+        <v>424</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>19</v>
+        <v>425</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>19</v>
+        <v>426</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>19</v>
+        <v>427</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>438</v>
+        <v>19</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>19</v>
       </c>
@@ -9432,22 +9587,22 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>441</v>
+        <v>104</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>19</v>
@@ -9464,10 +9619,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9490,18 +9645,16 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>443</v>
+        <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>444</v>
+        <v>201</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>445</v>
+        <v>202</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>446</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>19</v>
       </c>
@@ -9525,31 +9678,29 @@
         <v>19</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>405</v>
+        <v>19</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>447</v>
+        <v>19</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>448</v>
+        <v>19</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>442</v>
+        <v>115</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9561,19 +9712,19 @@
         <v>19</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>449</v>
+        <v>19</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>450</v>
+        <v>19</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>19</v>
@@ -9581,12 +9732,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>19</v>
       </c>
@@ -9607,18 +9760,16 @@
         <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>454</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>19</v>
       </c>
@@ -9666,31 +9817,31 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>451</v>
+        <v>115</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>216</v>
+        <v>282</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>455</v>
+        <v>19</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>19</v>
@@ -9698,10 +9849,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9712,7 +9863,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>19</v>
@@ -9724,20 +9875,16 @@
         <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>287</v>
+        <v>419</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>19</v>
       </c>
@@ -9785,31 +9932,31 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>293</v>
+        <v>19</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>460</v>
+        <v>19</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>19</v>
@@ -9817,10 +9964,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9837,23 +9984,25 @@
         <v>19</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>164</v>
+        <v>440</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>462</v>
+        <v>441</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O67" t="s" s="2">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>19</v>
@@ -9902,7 +10051,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9917,16 +10066,16 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>397</v>
+        <v>445</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>19</v>
@@ -9934,10 +10083,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9948,7 +10097,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
@@ -9957,20 +10106,22 @@
         <v>19</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="O68" t="s" s="2">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -9995,13 +10146,13 @@
         <v>19</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>19</v>
@@ -10019,13 +10170,13 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>19</v>
@@ -10034,16 +10185,16 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>363</v>
+        <v>452</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>150</v>
+        <v>453</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>19</v>
@@ -10051,10 +10202,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10077,17 +10228,17 @@
         <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>19</v>
@@ -10112,13 +10263,13 @@
         <v>19</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>19</v>
+        <v>460</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>19</v>
@@ -10136,7 +10287,7 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10145,22 +10296,22 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>476</v>
+        <v>19</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>150</v>
+        <v>463</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>19</v>
@@ -10168,10 +10319,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10194,16 +10345,20 @@
         <v>19</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>278</v>
+        <v>466</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
       </c>
@@ -10251,7 +10406,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10266,16 +10421,16 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>19</v>
+        <v>472</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>19</v>
@@ -10283,10 +10438,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10309,19 +10464,19 @@
         <v>19</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>428</v>
+        <v>474</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -10370,7 +10525,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10385,16 +10540,16 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>489</v>
+        <v>105</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>19</v>
+        <v>480</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>19</v>
@@ -10402,10 +10557,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10416,7 +10571,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>19</v>
@@ -10428,16 +10583,20 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>220</v>
+        <v>482</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>146</v>
+        <v>483</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
       </c>
@@ -10485,25 +10644,25 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>148</v>
+        <v>481</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>19</v>
+        <v>487</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>150</v>
+        <v>488</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>19</v>
@@ -10517,21 +10676,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>19</v>
@@ -10543,17 +10702,15 @@
         <v>19</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>222</v>
+        <v>102</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>19</v>
@@ -10602,22 +10759,22 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>19</v>
@@ -10634,14 +10791,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>438</v>
+        <v>107</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10654,26 +10811,24 @@
         <v>19</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>439</v>
+        <v>109</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>440</v>
+        <v>110</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>19</v>
       </c>
@@ -10721,7 +10876,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>441</v>
+        <v>115</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10733,10 +10888,10 @@
         <v>19</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>19</v>
@@ -10753,45 +10908,45 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>19</v>
+        <v>492</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>401</v>
+        <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="N75" t="s" s="2">
-        <v>496</v>
+        <v>111</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>497</v>
+        <v>246</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>19</v>
@@ -10816,13 +10971,13 @@
         <v>19</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>19</v>
@@ -10840,31 +10995,31 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>498</v>
+        <v>199</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>499</v>
+        <v>19</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>19</v>
@@ -10872,10 +11027,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10886,7 +11041,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>19</v>
@@ -10898,19 +11053,17 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>201</v>
+        <v>497</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>19</v>
@@ -10935,13 +11088,13 @@
         <v>19</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>19</v>
+        <v>501</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>19</v>
+        <v>502</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>19</v>
@@ -10959,13 +11112,13 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>19</v>
@@ -10974,16 +11127,16 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>507</v>
+        <v>105</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>19</v>
@@ -10991,21 +11144,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>510</v>
+        <v>19</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>19</v>
@@ -11017,18 +11170,18 @@
         <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>511</v>
+        <v>267</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>19</v>
       </c>
@@ -11076,13 +11229,13 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>19</v>
@@ -11091,16 +11244,16 @@
         <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>515</v>
+        <v>273</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>19</v>
@@ -11108,10 +11261,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11122,7 +11275,7 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>19</v>
@@ -11131,22 +11284,22 @@
         <v>19</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>472</v>
+        <v>341</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>521</v>
+        <v>345</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>19</v>
@@ -11195,13 +11348,13 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>19</v>
@@ -11210,16 +11363,16 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>477</v>
+        <v>347</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>522</v>
+        <v>105</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>19</v>
+        <v>514</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>19</v>
@@ -11227,10 +11380,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11241,31 +11394,29 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>428</v>
+        <v>223</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>19</v>
@@ -11314,13 +11465,13 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>19</v>
@@ -11329,16 +11480,16 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>528</v>
+        <v>452</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>19</v>
+        <v>519</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>19</v>
@@ -11346,10 +11497,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11372,16 +11523,18 @@
         <v>19</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>146</v>
+        <v>521</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>147</v>
+        <v>522</v>
       </c>
       <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>19</v>
       </c>
@@ -11405,13 +11558,13 @@
         <v>19</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>19</v>
+        <v>413</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>19</v>
+        <v>414</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>19</v>
@@ -11429,7 +11582,7 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>148</v>
+        <v>520</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11441,19 +11594,19 @@
         <v>19</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>150</v>
+        <v>415</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>19</v>
+        <v>524</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>19</v>
@@ -11461,21 +11614,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>19</v>
@@ -11487,18 +11640,18 @@
         <v>19</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>132</v>
+        <v>526</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>222</v>
+        <v>527</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>19</v>
       </c>
@@ -11546,31 +11699,31 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>154</v>
+        <v>525</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>19</v>
+        <v>530</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>150</v>
+        <v>531</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>19</v>
+        <v>532</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>19</v>
@@ -11578,46 +11731,42 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>438</v>
+        <v>19</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>132</v>
+        <v>332</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>439</v>
+        <v>534</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>19</v>
       </c>
@@ -11665,25 +11814,25 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>441</v>
+        <v>533</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>130</v>
+        <v>536</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>19</v>
@@ -11697,10 +11846,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11708,10 +11857,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>19</v>
@@ -11720,21 +11869,23 @@
         <v>19</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>533</v>
+        <v>482</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>19</v>
       </c>
@@ -11782,13 +11933,13 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>19</v>
@@ -11797,16 +11948,16 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>196</v>
+        <v>542</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>150</v>
+        <v>543</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>537</v>
+        <v>19</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>19</v>
@@ -11814,10 +11965,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11825,7 +11976,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>87</v>
@@ -11837,16 +11988,16 @@
         <v>19</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>539</v>
+        <v>102</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>540</v>
+        <v>103</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11873,13 +12024,13 @@
         <v>19</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>540</v>
+        <v>19</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>541</v>
+        <v>19</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>19</v>
@@ -11897,10 +12048,10 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>538</v>
+        <v>104</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>87</v>
@@ -11909,26 +12060,1438 @@
         <v>19</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK84" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AO84" t="s" s="2">
+      <c r="AK87" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO84">
+  <autoFilter ref="A1:AO96">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11938,7 +13501,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI95">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-VunsPatient.xlsx
+++ b/StructureDefinition-VunsPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T16:28:32+02:00</t>
+    <t>2025-08-18T11:20:46+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil pour un Patient enrôlé dans le cadre du projet Vers Un Souffle Nouveau</t>
+    <t>Profile for patient enrolled in the 'Vers Un Souffle Nouveau' project</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1183,7 +1183,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-PhoneNumber:Format des numéros de téléphone {matches('\\d+')}</t>
+PhoneNumber:Phone number format {matches('\\d+')}</t>
   </si>
   <si>
     <t>./url</t>
@@ -1278,7 +1278,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-Email:Format des emails {matches('\\S+@\\S+\\.\\S+')}</t>
+Email:Email format {matches('\\S+@\\S+\\.\\S+')}</t>
   </si>
   <si>
     <t>Patient.telecom:email.use</t>

--- a/StructureDefinition-VunsPatient.xlsx
+++ b/StructureDefinition-VunsPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-18T11:20:46+02:00</t>
+    <t>2025-08-26T14:51:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-VunsPatient.xlsx
+++ b/StructureDefinition-VunsPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T14:51:56+02:00</t>
+    <t>2025-09-10T16:13:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-VunsPatient.xlsx
+++ b/StructureDefinition-VunsPatient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-10T16:13:27+02:00</t>
+    <t>2025-09-12T12:04:03+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-VunsPatient.xlsx
+++ b/StructureDefinition-VunsPatient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-12T12:04:03+02:00</t>
+    <t>2025-09-12T14:17:00+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-VunsPatient.xlsx
+++ b/StructureDefinition-VunsPatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3599" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3561" uniqueCount="594">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-12T14:17:00+02:00</t>
+    <t>2026-02-04T18:27:09+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -437,7 +437,7 @@
     <t>Patient.meta.profile</t>
   </si>
   <si>
-    <t>4</t>
+    <t>3</t>
   </si>
   <si>
     <t xml:space="preserve">canonical(StructureDefinition)
@@ -482,15 +482,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/uv/ips/StructureDefinition/Patient-uv-ips</t>
-  </si>
-  <si>
-    <t>Patient.meta.profile:chulPatient</t>
-  </si>
-  <si>
-    <t>chulPatient</t>
-  </si>
-  <si>
-    <t>https://terminology.chuliege.be/fhir/StructureDefinition/chul-patient</t>
   </si>
   <si>
     <t>Patient.meta.security</t>
@@ -2191,7 +2182,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO96"/>
+  <dimension ref="A1:AO95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.40234375" customWidth="true" bestFit="true"/>
@@ -3768,20 +3759,18 @@
         <v>150</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>19</v>
@@ -3793,16 +3782,16 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3813,7 +3802,7 @@
         <v>19</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>19</v>
@@ -3828,13 +3817,13 @@
         <v>19</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>19</v>
@@ -3852,7 +3841,7 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3884,10 +3873,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3910,16 +3899,16 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3945,13 +3934,13 @@
         <v>19</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>19</v>
@@ -3969,7 +3958,7 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4001,10 +3990,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4015,28 +4004,28 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4062,13 +4051,13 @@
         <v>19</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>167</v>
+        <v>19</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
@@ -4086,13 +4075,13 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>19</v>
@@ -4118,10 +4107,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4138,22 +4127,22 @@
         <v>19</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4179,13 +4168,13 @@
         <v>19</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>19</v>
@@ -4203,7 +4192,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4235,14 +4224,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>19</v>
+        <v>182</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4261,16 +4250,16 @@
         <v>19</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4296,13 +4285,13 @@
         <v>19</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>182</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>19</v>
@@ -4320,7 +4309,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4335,7 +4324,7 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>19</v>
+        <v>188</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>19</v>
@@ -4352,21 +4341,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>19</v>
@@ -4378,16 +4367,16 @@
         <v>19</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4437,22 +4426,22 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>19</v>
@@ -4469,14 +4458,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4495,17 +4484,15 @@
         <v>19</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>19</v>
@@ -4542,19 +4529,17 @@
         <v>19</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4566,10 +4551,10 @@
         <v>19</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>19</v>
@@ -4586,12 +4571,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>19</v>
       </c>
@@ -4600,7 +4587,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>19</v>
@@ -4612,13 +4599,13 @@
         <v>19</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4657,17 +4644,19 @@
         <v>19</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4699,14 +4688,12 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>19</v>
       </c>
@@ -4727,13 +4714,13 @@
         <v>19</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>102</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
+        <v>103</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4784,22 +4771,22 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>203</v>
+        <v>104</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>19</v>
@@ -4830,7 +4817,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>19</v>
@@ -4842,13 +4829,13 @@
         <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>102</v>
+        <v>198</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4887,34 +4874,34 @@
         <v>19</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>211</v>
+        <v>19</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>19</v>
@@ -4931,10 +4918,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4942,10 +4929,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>19</v>
@@ -4957,22 +4944,24 @@
         <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>19</v>
+        <v>216</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>19</v>
@@ -5002,34 +4991,34 @@
         <v>19</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>115</v>
+        <v>217</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>19</v>
+        <v>196</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>19</v>
@@ -5046,10 +5035,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5072,24 +5061,22 @@
         <v>19</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>219</v>
+        <v>19</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>19</v>
@@ -5131,22 +5118,22 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>19</v>
+        <v>224</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>19</v>
@@ -5163,21 +5150,23 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>19</v>
@@ -5189,13 +5178,13 @@
         <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5246,22 +5235,22 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>19</v>
@@ -5278,13 +5267,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>19</v>
@@ -5306,13 +5295,13 @@
         <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5363,7 +5352,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5395,13 +5384,13 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>19</v>
@@ -5423,13 +5412,13 @@
         <v>19</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5480,7 +5469,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5512,16 +5501,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5534,13 +5521,13 @@
         <v>19</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>240</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>241</v>
@@ -5548,8 +5535,12 @@
       <c r="M29" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
       </c>
@@ -5597,7 +5588,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5612,7 +5603,7 @@
         <v>116</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>19</v>
+        <v>196</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>19</v>
@@ -5629,14 +5620,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5649,25 +5640,23 @@
         <v>19</v>
       </c>
       <c r="I30" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="J30" t="s" s="2">
-        <v>19</v>
-      </c>
       <c r="K30" t="s" s="2">
-        <v>108</v>
+        <v>246</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
@@ -5716,7 +5705,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5728,19 +5717,19 @@
         <v>19</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>19</v>
+        <v>251</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>19</v>
+        <v>253</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>19</v>
@@ -5748,10 +5737,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5762,34 +5751,38 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O31" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="Q31" s="2"/>
+      <c r="Q31" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="R31" t="s" s="2">
         <v>19</v>
       </c>
@@ -5833,13 +5826,13 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>19</v>
@@ -5848,16 +5841,16 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>256</v>
+        <v>19</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>19</v>
@@ -5865,10 +5858,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5876,109 +5869,107 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="Q32" t="s" s="2">
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="R32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>257</v>
-      </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>269</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>105</v>
+        <v>271</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>265</v>
+        <v>19</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>19</v>
+        <v>272</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>19</v>
@@ -5986,10 +5977,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5997,35 +5988,31 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G33" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G33" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H33" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>267</v>
+        <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>268</v>
+        <v>102</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>19</v>
       </c>
@@ -6073,31 +6060,31 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>266</v>
+        <v>104</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>272</v>
+        <v>19</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>273</v>
+        <v>105</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>275</v>
+        <v>19</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>19</v>
@@ -6105,21 +6092,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>19</v>
@@ -6131,15 +6118,17 @@
         <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -6176,31 +6165,31 @@
         <v>19</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>105</v>
@@ -6220,14 +6209,16 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="D35" t="s" s="2">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6246,17 +6237,15 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>108</v>
+        <v>277</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>109</v>
+        <v>278</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>19</v>
@@ -6293,16 +6282,16 @@
         <v>19</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>115</v>
@@ -6320,7 +6309,7 @@
         <v>116</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>105</v>
+        <v>279</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>19</v>
@@ -6337,14 +6326,12 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>19</v>
       </c>
@@ -6353,28 +6340,32 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>280</v>
+        <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>281</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
       </c>
@@ -6398,13 +6389,13 @@
         <v>19</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>19</v>
+        <v>286</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>19</v>
+        <v>287</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>19</v>
@@ -6422,22 +6413,22 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>115</v>
+        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>19</v>
@@ -6446,7 +6437,7 @@
         <v>19</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>19</v>
+        <v>290</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>19</v>
@@ -6454,10 +6445,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6474,25 +6465,25 @@
         <v>19</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6517,13 +6508,13 @@
         <v>19</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>289</v>
+        <v>19</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>290</v>
+        <v>19</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>19</v>
@@ -6541,7 +6532,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6556,7 +6547,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>19</v>
@@ -6565,7 +6556,7 @@
         <v>19</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>19</v>
@@ -6573,14 +6564,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>19</v>
+        <v>300</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6602,17 +6593,15 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>19</v>
       </c>
@@ -6624,7 +6613,7 @@
         <v>19</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>19</v>
+        <v>304</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>19</v>
@@ -6660,7 +6649,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6675,7 +6664,7 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>19</v>
@@ -6684,7 +6673,7 @@
         <v>19</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>19</v>
@@ -6692,21 +6681,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>19</v>
@@ -6721,13 +6710,13 @@
         <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6741,7 +6730,7 @@
         <v>19</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>19</v>
@@ -6777,13 +6766,13 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>19</v>
@@ -6792,7 +6781,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>19</v>
@@ -6801,7 +6790,7 @@
         <v>19</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>19</v>
@@ -6809,14 +6798,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>312</v>
+        <v>19</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6838,14 +6827,12 @@
         <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>19</v>
@@ -6894,7 +6881,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6909,7 +6896,7 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>19</v>
@@ -6918,7 +6905,7 @@
         <v>19</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>19</v>
@@ -6926,10 +6913,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6955,10 +6942,10 @@
         <v>101</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7009,7 +6996,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7024,7 +7011,7 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>19</v>
@@ -7033,7 +7020,7 @@
         <v>19</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>19</v>
@@ -7041,10 +7028,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7055,7 +7042,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>19</v>
@@ -7067,16 +7054,18 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>101</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
       </c>
@@ -7124,13 +7113,13 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>19</v>
@@ -7139,7 +7128,7 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>19</v>
@@ -7148,7 +7137,7 @@
         <v>19</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>19</v>
@@ -7156,10 +7145,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7167,10 +7156,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>19</v>
@@ -7182,17 +7171,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -7229,16 +7220,14 @@
         <v>19</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>336</v>
@@ -7247,7 +7236,7 @@
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>19</v>
@@ -7256,16 +7245,16 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>19</v>
+        <v>345</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>19</v>
@@ -7273,24 +7262,26 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>340</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>19</v>
@@ -7299,19 +7290,19 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
@@ -7348,17 +7339,19 @@
         <v>19</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7373,16 +7366,16 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>19</v>
@@ -7390,48 +7383,42 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="B45" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>351</v>
-      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G45" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H45" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>341</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>102</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>19</v>
       </c>
@@ -7479,31 +7466,31 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>339</v>
+        <v>104</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>347</v>
+        <v>105</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>348</v>
+        <v>19</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>349</v>
+        <v>19</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>19</v>
@@ -7511,21 +7498,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>19</v>
@@ -7537,15 +7524,17 @@
         <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>19</v>
@@ -7582,31 +7571,31 @@
         <v>19</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>105</v>
@@ -7626,21 +7615,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>19</v>
@@ -7649,20 +7638,18 @@
         <v>19</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>108</v>
+        <v>173</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>109</v>
+        <v>355</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -7672,7 +7659,7 @@
         <v>19</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>19</v>
+        <v>348</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>19</v>
@@ -7687,46 +7674,46 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>19</v>
+        <v>357</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>19</v>
+        <v>358</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>115</v>
+        <v>359</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>105</v>
+        <v>361</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>19</v>
@@ -7735,7 +7722,7 @@
         <v>19</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>19</v>
@@ -7743,10 +7730,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7754,7 +7741,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>87</v>
@@ -7769,16 +7756,20 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
       </c>
@@ -7787,7 +7778,7 @@
         <v>19</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>351</v>
+        <v>19</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>19</v>
@@ -7802,13 +7793,13 @@
         <v>19</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>19</v>
@@ -7826,7 +7817,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7835,13 +7826,13 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>363</v>
+        <v>19</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>370</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>19</v>
@@ -7850,7 +7841,7 @@
         <v>19</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>19</v>
@@ -7858,10 +7849,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7878,25 +7869,25 @@
         <v>19</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7921,13 +7912,13 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>19</v>
+        <v>379</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>19</v>
+        <v>380</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
@@ -7945,7 +7936,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7957,10 +7948,10 @@
         <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>373</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>374</v>
+        <v>289</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>19</v>
@@ -7969,7 +7960,7 @@
         <v>19</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>19</v>
@@ -7977,10 +7968,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7997,26 +7988,24 @@
         <v>19</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>176</v>
+        <v>385</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>19</v>
       </c>
@@ -8040,13 +8029,13 @@
         <v>19</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>382</v>
+        <v>19</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>383</v>
+        <v>19</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>19</v>
@@ -8064,7 +8053,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8079,7 +8068,7 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>292</v>
+        <v>105</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>19</v>
@@ -8088,7 +8077,7 @@
         <v>19</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>385</v>
+        <v>105</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>19</v>
@@ -8096,10 +8085,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8122,17 +8111,15 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>388</v>
+        <v>329</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -8181,7 +8168,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8196,7 +8183,7 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>105</v>
+        <v>334</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>19</v>
@@ -8205,7 +8192,7 @@
         <v>19</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>19</v>
@@ -8213,24 +8200,26 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>19</v>
@@ -8239,16 +8228,20 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>395</v>
+        <v>339</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
       </c>
@@ -8296,13 +8289,13 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>397</v>
+        <v>336</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>19</v>
@@ -8311,16 +8304,16 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>19</v>
+        <v>345</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>199</v>
+        <v>346</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>19</v>
@@ -8328,48 +8321,42 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>341</v>
+        <v>101</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>342</v>
+        <v>102</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>19</v>
       </c>
@@ -8417,31 +8404,31 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>339</v>
+        <v>104</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>347</v>
+        <v>105</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>348</v>
+        <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>349</v>
+        <v>19</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>19</v>
@@ -8449,21 +8436,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>19</v>
@@ -8475,15 +8462,17 @@
         <v>19</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -8520,31 +8509,31 @@
         <v>19</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>105</v>
@@ -8564,21 +8553,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>19</v>
@@ -8587,20 +8576,18 @@
         <v>19</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>108</v>
+        <v>173</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>109</v>
+        <v>355</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>19</v>
@@ -8610,7 +8597,7 @@
         <v>19</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>19</v>
+        <v>396</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>19</v>
@@ -8625,46 +8612,46 @@
         <v>19</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>19</v>
+        <v>357</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>19</v>
+        <v>358</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>115</v>
+        <v>359</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>105</v>
+        <v>361</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>19</v>
@@ -8673,7 +8660,7 @@
         <v>19</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>19</v>
@@ -8681,10 +8668,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8692,7 +8679,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>87</v>
@@ -8707,16 +8694,20 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>19</v>
       </c>
@@ -8725,7 +8716,7 @@
         <v>19</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>399</v>
+        <v>19</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>19</v>
@@ -8740,13 +8731,13 @@
         <v>19</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>19</v>
@@ -8764,7 +8755,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8773,13 +8764,13 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>363</v>
+        <v>19</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>401</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>19</v>
@@ -8788,7 +8779,7 @@
         <v>19</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>19</v>
@@ -8796,10 +8787,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8816,25 +8807,25 @@
         <v>19</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>19</v>
@@ -8859,13 +8850,13 @@
         <v>19</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>19</v>
+        <v>379</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>19</v>
+        <v>380</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
@@ -8883,7 +8874,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8895,10 +8886,10 @@
         <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>404</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>374</v>
+        <v>289</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>19</v>
@@ -8907,7 +8898,7 @@
         <v>19</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>19</v>
@@ -8915,10 +8906,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8935,26 +8926,24 @@
         <v>19</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>176</v>
+        <v>385</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>19</v>
       </c>
@@ -8978,13 +8967,13 @@
         <v>19</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>382</v>
+        <v>19</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>383</v>
+        <v>19</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>19</v>
@@ -9002,7 +8991,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9017,7 +9006,7 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>292</v>
+        <v>105</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>19</v>
@@ -9026,7 +9015,7 @@
         <v>19</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>385</v>
+        <v>105</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>19</v>
@@ -9034,10 +9023,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9060,17 +9049,15 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>388</v>
+        <v>329</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -9119,7 +9106,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9134,7 +9121,7 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>105</v>
+        <v>334</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>19</v>
@@ -9143,7 +9130,7 @@
         <v>19</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>19</v>
@@ -9151,10 +9138,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9162,13 +9149,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>19</v>
@@ -9177,16 +9164,20 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>332</v>
+        <v>173</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
       </c>
@@ -9210,13 +9201,13 @@
         <v>19</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>19</v>
+        <v>410</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>19</v>
+        <v>411</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>19</v>
@@ -9234,7 +9225,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9249,16 +9240,16 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>337</v>
+        <v>412</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>19</v>
+        <v>413</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>199</v>
+        <v>414</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>19</v>
@@ -9266,10 +9257,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9283,7 +9274,7 @@
         <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>19</v>
@@ -9292,19 +9283,19 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>176</v>
+        <v>416</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>19</v>
@@ -9329,13 +9320,13 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>413</v>
+        <v>19</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>414</v>
+        <v>19</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>19</v>
@@ -9353,7 +9344,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9368,27 +9359,27 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>19</v>
+        <v>424</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9396,7 +9387,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>87</v>
@@ -9408,23 +9399,19 @@
         <v>19</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>419</v>
+        <v>101</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>19</v>
       </c>
@@ -9472,7 +9459,7 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>418</v>
+        <v>104</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9484,22 +9471,22 @@
         <v>19</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>424</v>
+        <v>19</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>425</v>
+        <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>426</v>
+        <v>19</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>427</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" hidden="true">
@@ -9518,7 +9505,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>19</v>
@@ -9530,13 +9517,13 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>429</v>
+        <v>198</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>430</v>
+        <v>199</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9575,31 +9562,29 @@
         <v>19</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>19</v>
@@ -9619,12 +9604,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>19</v>
       </c>
@@ -9633,7 +9620,7 @@
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>19</v>
@@ -9645,13 +9632,13 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>108</v>
+        <v>277</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>201</v>
+        <v>431</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>202</v>
+        <v>431</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9690,14 +9677,16 @@
         <v>19</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC64" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>115</v>
@@ -9715,7 +9704,7 @@
         <v>116</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>19</v>
+        <v>279</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>19</v>
@@ -9735,11 +9724,9 @@
         <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>19</v>
       </c>
@@ -9760,10 +9747,10 @@
         <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>280</v>
+        <v>416</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>434</v>
@@ -9817,22 +9804,22 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>115</v>
+        <v>435</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>282</v>
+        <v>19</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>19</v>
@@ -9849,10 +9836,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9869,22 +9856,26 @@
         <v>19</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>19</v>
       </c>
@@ -9932,7 +9923,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9944,19 +9935,19 @@
         <v>19</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>19</v>
+        <v>442</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>19</v>
+        <v>443</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>19</v>
@@ -9964,10 +9955,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9978,31 +9969,31 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>440</v>
+        <v>220</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>19</v>
@@ -10051,13 +10042,13 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>19</v>
@@ -10066,16 +10057,16 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>105</v>
+        <v>450</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>19</v>
@@ -10083,10 +10074,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10097,7 +10088,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
@@ -10106,22 +10097,20 @@
         <v>19</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>223</v>
+        <v>453</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -10146,13 +10135,13 @@
         <v>19</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>19</v>
+        <v>457</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>19</v>
+        <v>458</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>19</v>
@@ -10170,13 +10159,13 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>19</v>
@@ -10185,16 +10174,16 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>19</v>
@@ -10202,10 +10191,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10228,17 +10217,19 @@
         <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O69" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>19</v>
@@ -10263,13 +10254,13 @@
         <v>19</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>460</v>
+        <v>19</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>461</v>
+        <v>19</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>19</v>
@@ -10287,7 +10278,7 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10302,16 +10293,16 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>463</v>
+        <v>105</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>19</v>
@@ -10319,10 +10310,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10333,7 +10324,7 @@
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>19</v>
@@ -10345,19 +10336,19 @@
         <v>19</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
@@ -10406,13 +10397,13 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>19</v>
@@ -10421,7 +10412,7 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>105</v>
@@ -10430,7 +10421,7 @@
         <v>19</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>19</v>
@@ -10438,10 +10429,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10464,19 +10455,19 @@
         <v>19</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -10525,7 +10516,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10537,10 +10528,10 @@
         <v>19</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>484</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>105</v>
@@ -10549,7 +10540,7 @@
         <v>19</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>480</v>
+        <v>19</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>19</v>
@@ -10557,10 +10548,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10571,7 +10562,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>19</v>
@@ -10583,20 +10574,16 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>482</v>
+        <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>483</v>
+        <v>102</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>19</v>
       </c>
@@ -10644,25 +10631,25 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>481</v>
+        <v>104</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>487</v>
+        <v>19</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>488</v>
+        <v>105</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>19</v>
@@ -10676,21 +10663,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>19</v>
@@ -10702,15 +10689,17 @@
         <v>19</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>19</v>
@@ -10759,19 +10748,19 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>105</v>
@@ -10791,14 +10780,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>107</v>
+        <v>489</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10811,24 +10800,26 @@
         <v>19</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>109</v>
+        <v>490</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>110</v>
+        <v>491</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>19</v>
       </c>
@@ -10876,7 +10867,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>115</v>
+        <v>492</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10891,7 +10882,7 @@
         <v>116</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>19</v>
@@ -10908,14 +10899,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>492</v>
+        <v>19</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10928,25 +10919,23 @@
         <v>19</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>108</v>
+        <v>494</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>246</v>
+        <v>497</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>19</v>
@@ -10971,13 +10960,13 @@
         <v>19</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>19</v>
+        <v>498</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>19</v>
+        <v>499</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>19</v>
@@ -10995,7 +10984,7 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11007,19 +10996,19 @@
         <v>19</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>199</v>
+        <v>500</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>19</v>
+        <v>501</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>19</v>
@@ -11027,10 +11016,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11041,7 +11030,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>19</v>
@@ -11053,17 +11042,17 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>497</v>
+        <v>264</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>19</v>
@@ -11088,37 +11077,37 @@
         <v>19</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>501</v>
+        <v>19</v>
       </c>
       <c r="Z76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AA76" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>496</v>
-      </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>19</v>
@@ -11127,7 +11116,7 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>503</v>
+        <v>270</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>105</v>
@@ -11136,7 +11125,7 @@
         <v>19</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>19</v>
@@ -11144,10 +11133,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11158,7 +11147,7 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>19</v>
@@ -11170,17 +11159,19 @@
         <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>267</v>
+        <v>338</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="O77" t="s" s="2">
-        <v>508</v>
+        <v>342</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>19</v>
@@ -11229,13 +11220,13 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>19</v>
@@ -11244,7 +11235,7 @@
         <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>273</v>
+        <v>344</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>105</v>
@@ -11253,7 +11244,7 @@
         <v>19</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>19</v>
@@ -11261,10 +11252,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11275,7 +11266,7 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>19</v>
@@ -11287,19 +11278,17 @@
         <v>19</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>341</v>
+        <v>220</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>345</v>
+        <v>515</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>19</v>
@@ -11348,13 +11337,13 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>19</v>
@@ -11363,7 +11352,7 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>347</v>
+        <v>449</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>105</v>
@@ -11372,7 +11361,7 @@
         <v>19</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>19</v>
@@ -11380,10 +11369,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11406,17 +11395,17 @@
         <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>19</v>
@@ -11441,13 +11430,13 @@
         <v>19</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>19</v>
+        <v>410</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>19</v>
+        <v>411</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>19</v>
@@ -11465,7 +11454,7 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11480,7 +11469,7 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>452</v>
+        <v>412</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>105</v>
@@ -11489,7 +11478,7 @@
         <v>19</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>19</v>
@@ -11497,10 +11486,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11523,17 +11512,17 @@
         <v>19</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>176</v>
+        <v>523</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>19</v>
@@ -11558,13 +11547,13 @@
         <v>19</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>413</v>
+        <v>19</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>414</v>
+        <v>19</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>19</v>
@@ -11582,7 +11571,7 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11591,13 +11580,13 @@
         <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>19</v>
+        <v>527</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>415</v>
+        <v>528</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>105</v>
@@ -11606,7 +11595,7 @@
         <v>19</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>19</v>
@@ -11614,10 +11603,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11640,18 +11629,16 @@
         <v>19</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>526</v>
+        <v>329</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>529</v>
-      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>19</v>
       </c>
@@ -11699,7 +11686,7 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11708,13 +11695,13 @@
         <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>530</v>
+        <v>19</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>105</v>
@@ -11723,7 +11710,7 @@
         <v>19</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>532</v>
+        <v>19</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>19</v>
@@ -11731,10 +11718,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11745,7 +11732,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>19</v>
@@ -11757,16 +11744,20 @@
         <v>19</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>332</v>
+        <v>479</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>19</v>
       </c>
@@ -11814,13 +11805,13 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>19</v>
@@ -11829,10 +11820,10 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>105</v>
+        <v>540</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>19</v>
@@ -11846,10 +11837,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11860,7 +11851,7 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>19</v>
@@ -11872,20 +11863,16 @@
         <v>19</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>482</v>
+        <v>101</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>538</v>
+        <v>102</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>541</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>19</v>
       </c>
@@ -11933,25 +11920,25 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>537</v>
+        <v>104</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>542</v>
+        <v>105</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>543</v>
+        <v>19</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>19</v>
@@ -11965,21 +11952,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>19</v>
@@ -11991,15 +11978,17 @@
         <v>19</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>19</v>
@@ -12048,19 +12037,19 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>105</v>
@@ -12080,14 +12069,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>107</v>
+        <v>489</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12100,24 +12089,26 @@
         <v>19</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>109</v>
+        <v>490</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>110</v>
+        <v>491</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>19</v>
       </c>
@@ -12165,7 +12156,7 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>115</v>
+        <v>492</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12180,7 +12171,7 @@
         <v>116</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>19</v>
@@ -12197,45 +12188,45 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>492</v>
+        <v>19</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>108</v>
+        <v>453</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>493</v>
+        <v>545</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>494</v>
+        <v>546</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>111</v>
+        <v>547</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>246</v>
+        <v>548</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>19</v>
@@ -12260,13 +12251,13 @@
         <v>19</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>19</v>
@@ -12284,31 +12275,31 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>495</v>
+        <v>544</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>199</v>
+        <v>549</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>19</v>
+        <v>550</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>19</v>
+        <v>551</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>19</v>
@@ -12316,10 +12307,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12327,7 +12318,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>87</v>
@@ -12342,19 +12333,19 @@
         <v>19</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>456</v>
+        <v>255</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>19</v>
@@ -12379,13 +12370,13 @@
         <v>19</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>182</v>
+        <v>19</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>19</v>
@@ -12403,10 +12394,10 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>87</v>
@@ -12418,16 +12409,16 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>19</v>
@@ -12435,21 +12426,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>19</v>
+        <v>561</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>19</v>
@@ -12461,20 +12452,18 @@
         <v>19</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>19</v>
       </c>
@@ -12522,13 +12511,13 @@
         <v>19</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>19</v>
@@ -12537,16 +12526,16 @@
         <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>561</v>
+        <v>105</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>19</v>
@@ -12554,21 +12543,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>564</v>
+        <v>19</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>19</v>
@@ -12577,21 +12566,23 @@
         <v>19</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>565</v>
+        <v>523</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>19</v>
       </c>
@@ -12639,13 +12630,13 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>19</v>
@@ -12654,16 +12645,16 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>569</v>
+        <v>528</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>105</v>
+        <v>573</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>570</v>
+        <v>19</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>19</v>
@@ -12671,10 +12662,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12685,31 +12676,31 @@
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>526</v>
+        <v>479</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>19</v>
@@ -12758,13 +12749,13 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>19</v>
@@ -12773,10 +12764,10 @@
         <v>99</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>531</v>
+        <v>579</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>576</v>
+        <v>105</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>19</v>
@@ -12790,10 +12781,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12804,32 +12795,28 @@
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>482</v>
+        <v>101</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>578</v>
+        <v>102</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>581</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>19</v>
       </c>
@@ -12877,25 +12864,25 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>577</v>
+        <v>104</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>582</v>
+        <v>105</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>19</v>
@@ -12909,21 +12896,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>19</v>
@@ -12935,15 +12922,17 @@
         <v>19</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>19</v>
@@ -12992,19 +12981,19 @@
         <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>105</v>
@@ -13024,14 +13013,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>107</v>
+        <v>489</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13044,24 +13033,26 @@
         <v>19</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>109</v>
+        <v>490</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>110</v>
+        <v>491</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O93" s="2"/>
+      <c r="O93" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>19</v>
       </c>
@@ -13109,7 +13100,7 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>115</v>
+        <v>492</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13124,7 +13115,7 @@
         <v>116</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>19</v>
@@ -13141,46 +13132,44 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>492</v>
+        <v>19</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>108</v>
+        <v>584</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>493</v>
+        <v>585</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>494</v>
+        <v>586</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>19</v>
       </c>
@@ -13228,31 +13217,31 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>495</v>
+        <v>583</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>19</v>
+        <v>588</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>19</v>
@@ -13260,10 +13249,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13286,17 +13275,15 @@
         <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>587</v>
+        <v>173</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>19</v>
@@ -13321,13 +13308,13 @@
         <v>19</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>19</v>
+        <v>591</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>19</v>
+        <v>592</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>19</v>
@@ -13345,7 +13332,7 @@
         <v>19</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>87</v>
@@ -13360,7 +13347,7 @@
         <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>253</v>
+        <v>593</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>105</v>
@@ -13369,129 +13356,14 @@
         <v>19</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>591</v>
+        <v>19</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AO96" t="s" s="2">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO96">
+  <autoFilter ref="A1:AO95">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13501,7 +13373,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI95">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
